--- a/public/templates/lp_import_template.xlsx
+++ b/public/templates/lp_import_template.xlsx
@@ -42,8 +42,7 @@
       <sz val="10"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
@@ -101,10 +100,10 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -472,34 +471,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>* = Required field  |  Blue = Required  |  Gray = Optional  |  Do not modify column headers</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
+          <t>* = Required  |  Blue = Required  |  Gray = Optional  |  Called Capital &amp; Distributions: enter existing balances when migrating from another system</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Investor Name*</t>
@@ -522,55 +523,65 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>Called Capital</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Distributions</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>Commitment Date</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Address Line 1</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>Address Line 2</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>ZIP Code</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>Contact Name</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -595,59 +606,65 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>15/01/2024</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>john@smithfamily.com</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>+1 (415) 555-0100</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>123 Main Street</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>Suite 100</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>California</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>94105</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>John Smith</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>Lead investor</t>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>Lead investor — 2 calls made so far</t>
         </is>
       </c>
     </row>
@@ -666,49 +683,120 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="4" t="n">
+        <v>250000</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>01/03/2024</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>raj@example.com</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>+91 98765 43210</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>Plot 12, Koramangala</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="n"/>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
         </is>
       </c>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="inlineStr">
         <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
           <t>560034</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="N4" s="4" t="n"/>
-      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="n"/>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>Fully called, partial distribution received</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>New LP - No calls yet</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n">
+        <v>500000</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>newlp@example.com</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>+1 (650) 555-0200</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>Texas</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>78701</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="n"/>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>Committed but no capital called yet</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -720,16 +808,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Field</t>
@@ -742,16 +829,11 @@
       </c>
       <c r="C1" s="5" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>Example</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+          <t>Description / Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Investor Name</t>
@@ -767,13 +849,8 @@
           <t>Full legal name of the LP</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>Smith Family Office</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+    </row>
+    <row r="3" ht="36" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Investing As</t>
@@ -786,16 +863,11 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Legal entity name they invest through</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Smith Family Trust</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>Legal entity they invest through (trust, LLC, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Commitment Amount</t>
@@ -808,16 +880,11 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Total pledged amount as a number</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+          <t>Total pledged amount — number only, e.g. 5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Currency</t>
@@ -830,254 +897,228 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Three-letter currency code</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+          <t>USD, EUR, GBP, INR, SGD, AED</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
+          <t>Called Capital</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Total already called from this LP. Leave blank for new LPs. Used when migrating existing data — creates an opening balance transaction automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Distributions</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Total already distributed back to this LP. Leave blank if none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
           <t>Commitment Date</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Date of commitment (dd/mm/yyyy)</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>15/01/2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>Primary contact email</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>john@smithfamily.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Phone number with country code</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>+1 (415) 555-0100</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Phone with country code, e.g. +1 (415) 555-0100</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Address Line 1</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Street address</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>123 Main Street</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Address Line 2</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Suite, apt, floor etc.</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Suite 100</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Suite, apt, floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>State or province</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>California</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>ZIP Code</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Postal/ZIP code</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>94105</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Postal / ZIP code</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Country name</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Country name, e.g. USA, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Contact Name</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Primary contact person name</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>John Smith</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>Any additional notes</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>Lead investor</t>
         </is>
       </c>
     </row>

--- a/public/templates/lp_import_template.xlsx
+++ b/public/templates/lp_import_template.xlsx
@@ -27,25 +27,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <i val="1"/>
-      <color rgb="009b9890"/>
+      <color rgb="006B6860"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <name val="Arial"/>
+      <sz val="9"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00888888"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <name val="Arial"/>
+      <color rgb="001A1915"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -54,17 +57,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002d5be3"/>
+        <fgColor rgb="002D5BE3"/>
+        <bgColor rgb="002D5BE3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="006b6860"/>
+        <fgColor rgb="006B6860"/>
+        <bgColor rgb="006B6860"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4F3EF"/>
+        <fgColor rgb="00F9F8F5"/>
+        <bgColor rgb="00F9F8F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,33 +89,45 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="00E8E6DF"/>
+      </left>
       <right style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00E8E6DF"/>
       </right>
+      <top style="thin">
+        <color rgb="00E8E6DF"/>
+      </top>
       <bottom style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00E8E6DF"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -471,26 +495,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:R50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="28" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -500,7 +525,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Investor Name*</t>
@@ -508,295 +533,1219 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Investing As</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+          <t>Investor Type</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Entity Name</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Commitment Amount*</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Currency*</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Called Capital</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Distributions</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Commitment Date</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>GP Contact</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>Address Line 1</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>Address Line 2</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>ZIP Code</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>Contact Name</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1">
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Smith Family Office</t>
+          <t>John Smith</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Smith Family Trust</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr"/>
+      <c r="D3" s="4" t="n">
+        <v>500000</v>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E3" s="4" t="n">
-        <v>4000000</v>
-      </c>
       <c r="F3" s="4" t="n">
+        <v>400000</v>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>15/01/2024</t>
-        </is>
-      </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
+          <t>01/15/2024</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
           <t>john@smithfamily.com</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>+1 (415) 555-0100</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Mohan Verma</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>123 Main Street</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>Suite 100</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>California</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>94105</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>John Smith</t>
-        </is>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>Lead investor — 2 calls made so far</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
+      <c r="R3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Raj Patel</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n">
+          <t>Raj Arora</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Institution</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Arora Family Trust</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
         <v>250000</v>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="F4" s="4" t="n">
         <v>250000</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="G4" s="4" t="n">
         <v>50000</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>01/03/2024</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>raj@example.com</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>+91 98765 43210</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Kishore Mokada</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>Plot 12, Koramangala</t>
         </is>
       </c>
-      <c r="K4" s="4" t="n"/>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>Bangalore</t>
         </is>
       </c>
-      <c r="M4" s="4" t="n"/>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>560034</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="P4" s="4" t="n"/>
-      <c r="Q4" s="4" t="inlineStr">
-        <is>
-          <t>Fully called, partial distribution received</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
+      <c r="R4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>New LP - No calls yet</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n">
+          <t>New LP</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="n">
         <v>500000</v>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>newlp@example.com</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>+1 (650) 555-0200</t>
         </is>
       </c>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>Austin</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>Texas</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>78701</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="P5" s="4" t="n"/>
-      <c r="Q5" s="4" t="inlineStr">
-        <is>
-          <t>Committed but no capital called yet</t>
-        </is>
-      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>No calls yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
+      <c r="Q6" s="5" t="n"/>
+      <c r="R6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
+      <c r="Q7" s="5" t="n"/>
+      <c r="R7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
+      <c r="Q8" s="5" t="n"/>
+      <c r="R8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
+      <c r="Q9" s="5" t="n"/>
+      <c r="R9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
+      <c r="Q10" s="5" t="n"/>
+      <c r="R10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
+      <c r="Q11" s="5" t="n"/>
+      <c r="R11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
+      <c r="Q12" s="5" t="n"/>
+      <c r="R12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
+      <c r="Q13" s="5" t="n"/>
+      <c r="R13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
+      <c r="Q14" s="5" t="n"/>
+      <c r="R14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="5" t="n"/>
+      <c r="Q15" s="5" t="n"/>
+      <c r="R15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+      <c r="P16" s="5" t="n"/>
+      <c r="Q16" s="5" t="n"/>
+      <c r="R16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+      <c r="P17" s="5" t="n"/>
+      <c r="Q17" s="5" t="n"/>
+      <c r="R17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
+      <c r="Q18" s="5" t="n"/>
+      <c r="R18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
+      <c r="Q19" s="5" t="n"/>
+      <c r="R19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="5" t="n"/>
+      <c r="Q20" s="5" t="n"/>
+      <c r="R20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
+      <c r="Q21" s="5" t="n"/>
+      <c r="R21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+      <c r="P22" s="5" t="n"/>
+      <c r="Q22" s="5" t="n"/>
+      <c r="R22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+      <c r="P23" s="5" t="n"/>
+      <c r="Q23" s="5" t="n"/>
+      <c r="R23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+      <c r="P24" s="5" t="n"/>
+      <c r="Q24" s="5" t="n"/>
+      <c r="R24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+      <c r="P25" s="5" t="n"/>
+      <c r="Q25" s="5" t="n"/>
+      <c r="R25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
+      <c r="P26" s="5" t="n"/>
+      <c r="Q26" s="5" t="n"/>
+      <c r="R26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+      <c r="P27" s="5" t="n"/>
+      <c r="Q27" s="5" t="n"/>
+      <c r="R27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+      <c r="P28" s="5" t="n"/>
+      <c r="Q28" s="5" t="n"/>
+      <c r="R28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="5" t="n"/>
+      <c r="P29" s="5" t="n"/>
+      <c r="Q29" s="5" t="n"/>
+      <c r="R29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="n"/>
+      <c r="P30" s="5" t="n"/>
+      <c r="Q30" s="5" t="n"/>
+      <c r="R30" s="5" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="n"/>
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="n"/>
+      <c r="O31" s="5" t="n"/>
+      <c r="P31" s="5" t="n"/>
+      <c r="Q31" s="5" t="n"/>
+      <c r="R31" s="5" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="5" t="n"/>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="n"/>
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
+      <c r="P32" s="5" t="n"/>
+      <c r="Q32" s="5" t="n"/>
+      <c r="R32" s="5" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
+      <c r="Q33" s="5" t="n"/>
+      <c r="R33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="5" t="n"/>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="n"/>
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="5" t="n"/>
+      <c r="O34" s="5" t="n"/>
+      <c r="P34" s="5" t="n"/>
+      <c r="Q34" s="5" t="n"/>
+      <c r="R34" s="5" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="5" t="n"/>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="n"/>
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="5" t="n"/>
+      <c r="O35" s="5" t="n"/>
+      <c r="P35" s="5" t="n"/>
+      <c r="Q35" s="5" t="n"/>
+      <c r="R35" s="5" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="5" t="n"/>
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="n"/>
+      <c r="N36" s="5" t="n"/>
+      <c r="O36" s="5" t="n"/>
+      <c r="P36" s="5" t="n"/>
+      <c r="Q36" s="5" t="n"/>
+      <c r="R36" s="5" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="n"/>
+      <c r="O37" s="5" t="n"/>
+      <c r="P37" s="5" t="n"/>
+      <c r="Q37" s="5" t="n"/>
+      <c r="R37" s="5" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="5" t="n"/>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="5" t="n"/>
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="n"/>
+      <c r="O38" s="5" t="n"/>
+      <c r="P38" s="5" t="n"/>
+      <c r="Q38" s="5" t="n"/>
+      <c r="R38" s="5" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="5" t="n"/>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="5" t="n"/>
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="n"/>
+      <c r="N39" s="5" t="n"/>
+      <c r="O39" s="5" t="n"/>
+      <c r="P39" s="5" t="n"/>
+      <c r="Q39" s="5" t="n"/>
+      <c r="R39" s="5" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="5" t="n"/>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="n"/>
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="5" t="n"/>
+      <c r="N40" s="5" t="n"/>
+      <c r="O40" s="5" t="n"/>
+      <c r="P40" s="5" t="n"/>
+      <c r="Q40" s="5" t="n"/>
+      <c r="R40" s="5" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="5" t="n"/>
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="n"/>
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="5" t="n"/>
+      <c r="N41" s="5" t="n"/>
+      <c r="O41" s="5" t="n"/>
+      <c r="P41" s="5" t="n"/>
+      <c r="Q41" s="5" t="n"/>
+      <c r="R41" s="5" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="5" t="n"/>
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="n"/>
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="n"/>
+      <c r="N42" s="5" t="n"/>
+      <c r="O42" s="5" t="n"/>
+      <c r="P42" s="5" t="n"/>
+      <c r="Q42" s="5" t="n"/>
+      <c r="R42" s="5" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="5" t="n"/>
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="n"/>
+      <c r="L43" s="5" t="n"/>
+      <c r="M43" s="5" t="n"/>
+      <c r="N43" s="5" t="n"/>
+      <c r="O43" s="5" t="n"/>
+      <c r="P43" s="5" t="n"/>
+      <c r="Q43" s="5" t="n"/>
+      <c r="R43" s="5" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="5" t="n"/>
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="n"/>
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="n"/>
+      <c r="K44" s="5" t="n"/>
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+      <c r="N44" s="5" t="n"/>
+      <c r="O44" s="5" t="n"/>
+      <c r="P44" s="5" t="n"/>
+      <c r="Q44" s="5" t="n"/>
+      <c r="R44" s="5" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="5" t="n"/>
+      <c r="B45" s="5" t="n"/>
+      <c r="C45" s="5" t="n"/>
+      <c r="D45" s="5" t="n"/>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="n"/>
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="5" t="n"/>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="n"/>
+      <c r="K45" s="5" t="n"/>
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="n"/>
+      <c r="O45" s="5" t="n"/>
+      <c r="P45" s="5" t="n"/>
+      <c r="Q45" s="5" t="n"/>
+      <c r="R45" s="5" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="5" t="n"/>
+      <c r="B46" s="5" t="n"/>
+      <c r="C46" s="5" t="n"/>
+      <c r="D46" s="5" t="n"/>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="n"/>
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="n"/>
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="n"/>
+      <c r="O46" s="5" t="n"/>
+      <c r="P46" s="5" t="n"/>
+      <c r="Q46" s="5" t="n"/>
+      <c r="R46" s="5" t="n"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="5" t="n"/>
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="n"/>
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+      <c r="N47" s="5" t="n"/>
+      <c r="O47" s="5" t="n"/>
+      <c r="P47" s="5" t="n"/>
+      <c r="Q47" s="5" t="n"/>
+      <c r="R47" s="5" t="n"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="5" t="n"/>
+      <c r="B48" s="5" t="n"/>
+      <c r="C48" s="5" t="n"/>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
+      <c r="K48" s="5" t="n"/>
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="n"/>
+      <c r="O48" s="5" t="n"/>
+      <c r="P48" s="5" t="n"/>
+      <c r="Q48" s="5" t="n"/>
+      <c r="R48" s="5" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="5" t="n"/>
+      <c r="B49" s="5" t="n"/>
+      <c r="C49" s="5" t="n"/>
+      <c r="D49" s="5" t="n"/>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="n"/>
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="5" t="n"/>
+      <c r="I49" s="5" t="n"/>
+      <c r="J49" s="5" t="n"/>
+      <c r="K49" s="5" t="n"/>
+      <c r="L49" s="5" t="n"/>
+      <c r="M49" s="5" t="n"/>
+      <c r="N49" s="5" t="n"/>
+      <c r="O49" s="5" t="n"/>
+      <c r="P49" s="5" t="n"/>
+      <c r="Q49" s="5" t="n"/>
+      <c r="R49" s="5" t="n"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="5" t="n"/>
+      <c r="B50" s="5" t="n"/>
+      <c r="C50" s="5" t="n"/>
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="n"/>
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="5" t="n"/>
+      <c r="I50" s="5" t="n"/>
+      <c r="J50" s="5" t="n"/>
+      <c r="K50" s="5" t="n"/>
+      <c r="L50" s="5" t="n"/>
+      <c r="M50" s="5" t="n"/>
+      <c r="N50" s="5" t="n"/>
+      <c r="O50" s="5" t="n"/>
+      <c r="P50" s="5" t="n"/>
+      <c r="Q50" s="5" t="n"/>
+      <c r="R50" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A1:R1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -808,317 +1757,238 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Required?</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>Description / Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Investor Name</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>Full legal name of the LP</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Investing As</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Legal entity they invest through (trust, LLC, etc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Commitment Amount</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Total pledged amount — number only, e.g. 5000000</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>USD, EUR, GBP, INR, SGD, AED</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Investor Name*</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Required. Full name of the investor (individual or contact person for entities).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Investor Type</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Optional. One of: Individual, Institution, Family Office, Corporate. Defaults to Individual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Entity Name</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Required if Investor Type is Institution/Family Office/Corporate. Legal entity name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Commitment Amount*</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Required. Total commitment in USD (numbers only, no $ sign).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Currency*</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Required. Use USD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Called Capital</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Total already called from this LP. Leave blank for new LPs. Used when migrating existing data — creates an opening balance transaction automatically.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Optional. Amount already called. Used to create an opening balance transaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Distributions</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Total already distributed back to this LP. Leave blank if none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Optional. Total distributions received to date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Commitment Date</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Date of commitment (dd/mm/yyyy)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Optional. Format: DD/MM/YYYY or YYYY-MM-DD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Primary contact email</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Optional. Investor email address.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Phone with country code, e.g. +1 (415) 555-0100</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Optional. Include country code e.g. +1 (415) 555-0100.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>GP Contact</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Optional. Name of the GP who sourced this LP (must match GP name in the fund).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Address Line 1</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Street address</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Optional. Street address.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Address Line 2</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Suite, apt, floor</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Optional. Suite, apt, floor etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Optional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>State or province</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Optional. Full state name e.g. California, or abbreviation e.g. CA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>ZIP Code</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Postal / ZIP code</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Optional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Country name, e.g. USA, India</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Contact Name</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Primary contact person name</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Optional. Defaults to USA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Any additional notes</t>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Optional. Any additional notes about this investor.</t>
         </is>
       </c>
     </row>

--- a/public/templates/lp_import_template.xlsx
+++ b/public/templates/lp_import_template.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,25 +27,50 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <i val="1"/>
-      <color rgb="009b9890"/>
+      <color rgb="00666666"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00888888"/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00444444"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00CC0000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00666666"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -59,16 +84,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="006b6860"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4F3EF"/>
+        <fgColor rgb="00A0A0A0"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -76,36 +96,27 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -471,36 +482,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="28" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>* = Required  |  Blue = Required  |  Gray = Optional  |  Called Capital &amp; Distributions: enter existing balances when migrating from another system</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Investor Name*</t>
@@ -508,295 +520,291 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Investing As</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+          <t>Investor Type</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Entity Name</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Commitment Amount*</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Currency*</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Called Capital</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Distributions</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Commitment Date</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>GP Contact</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>Address Line 1</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>Address Line 2</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>ZIP Code</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>Contact Name</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1">
+    <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Smith Family Office</t>
+          <t>Jack Cheng</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Smith Family Trust</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr"/>
+      <c r="D3" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E3" s="4" t="n">
-        <v>4000000</v>
-      </c>
       <c r="F3" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>15/01/2024</t>
-        </is>
-      </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>john@smithfamily.com</t>
+          <t>01/03/2024</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>+1 (415) 555-0100</t>
+          <t>jack@gmail.com</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>123 Main Street</t>
+          <t>408-123-5678</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>Suite 100</t>
+          <t>Mohan Verma</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>California</t>
-        </is>
-      </c>
+          <t>46 Adir Way</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr"/>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>94105</t>
+          <t>Hayward</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>94542</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>John Smith</t>
-        </is>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>Lead investor — 2 calls made so far</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
+      <c r="R3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Raj Patel</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
+          <t>David Family Trust</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Institution</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>David Family Trust</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>250000</v>
-      </c>
       <c r="F4" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>01/03/2024</t>
-        </is>
+        <v>100000</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>raj@example.com</t>
+          <t>15/06/2024</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>+91 98765 43210</t>
+          <t>david@gmail.com</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Plot 12, Koramangala</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="n"/>
+          <t>510-234-4567</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Kishore Mokada</t>
+        </is>
+      </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="n"/>
+          <t>245 Main St</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr"/>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>560034</t>
+          <t>San Jose</t>
         </is>
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="n"/>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>95112</t>
+        </is>
+      </c>
       <c r="Q4" s="4" t="inlineStr">
         <is>
-          <t>Fully called, partial distribution received</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>New LP - No calls yet</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n">
+          <t>New LP</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="n">
         <v>500000</v>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>newlp@example.com</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>+1 (650) 555-0200</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>Austin</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>Texas</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>78701</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr"/>
+      <c r="O5" s="4" t="inlineStr"/>
+      <c r="P5" s="4" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="P5" s="4" t="n"/>
-      <c r="Q5" s="4" t="inlineStr">
-        <is>
-          <t>Committed but no capital called yet</t>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>Committed but not yet called</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A1:R1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -808,18 +816,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
+    <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>Column</t>
         </is>
       </c>
       <c r="B1" s="5" t="inlineStr">
@@ -833,292 +841,305 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="18" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Investor Name</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
+          <t>Investor Name*</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>Full legal name of the LP</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Full name of the investor (individual or primary contact for entities).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Investing As</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Legal entity they invest through (trust, LLC, etc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
+          <t>Investor Type</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>One of: Individual, Institution, Family Office, Corporate. Defaults to Individual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Commitment Amount</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
+          <t>Entity Name</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Required if Investor Type is Institution/Family Office/Corporate. Legal entity name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Commitment Amount*</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Total pledged amount — number only, e.g. 5000000</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Total commitment in USD (numbers only, no $ sign). E.g. 100000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Currency*</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>USD, EUR, GBP, INR, SGD, AED</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Use USD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Called Capital</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Total already called from this LP. Leave blank for new LPs. Used when migrating existing data — creates an opening balance transaction automatically.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Amount already called. Leave blank for new LPs with no prior calls. Creates an opening balance transaction when importing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Distributions</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Total already distributed back to this LP. Leave blank if none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Total distributions received to date. Leave blank if none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Commitment Date</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Date of commitment (dd/mm/yyyy)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Format: DD/MM/YYYY or YYYY-MM-DD. E.g. 01/03/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Primary contact email</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Investor email address.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Phone with country code, e.g. +1 (415) 555-0100</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Include country code. E.g. +1 (415) 555-0100</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>GP Contact</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Name of the GP who sourced this LP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Address Line 1</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Street address</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Street address.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Address Line 2</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Suite, apt, floor</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Suite, apt, floor etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>State or province</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Full name or abbreviation. E.g. California or CA</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>ZIP Code</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Postal / ZIP code</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Postal / ZIP code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Country name, e.g. USA, India</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Contact Name</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Primary contact person name</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Defaults to USA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Any additional notes</t>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Any additional notes about this investor.</t>
         </is>
       </c>
     </row>
